--- a/AAII_Financials/Quarterly/SFGYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SFGYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="92">
   <si>
     <t>SFGYY</t>
   </si>
@@ -656,59 +656,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44286</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44104</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44012</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43830</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43738</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -739,8 +742,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -771,8 +777,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -803,8 +812,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -817,8 +829,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -849,8 +862,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -881,8 +897,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -913,8 +932,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -945,8 +967,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -956,8 +981,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -988,8 +1014,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1020,8 +1049,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1034,8 +1066,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1066,8 +1099,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1098,8 +1134,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1130,8 +1169,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1162,8 +1204,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1194,8 +1239,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1226,8 +1274,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1258,8 +1309,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1290,8 +1344,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1322,8 +1379,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1354,8 +1414,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1386,8 +1449,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1418,8 +1484,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1450,8 +1519,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1482,8 +1554,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1514,8 +1589,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1546,45 +1624,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44286</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44104</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44012</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43830</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43738</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1597,8 +1681,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1611,40 +1696,44 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2305800</v>
+      </c>
+      <c r="E41" s="3">
         <v>5716500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4495500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4817500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5768700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5191900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5111100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4196200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4159000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4791200</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1675,23 +1764,26 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>559200</v>
+      </c>
+      <c r="E43" s="3">
         <v>269900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>28600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>30600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>4</v>
       </c>
@@ -1707,8 +1799,11 @@
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1739,168 +1834,186 @@
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>471000</v>
+      </c>
+      <c r="E45" s="3">
         <v>223900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>46600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>50000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>39400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>43800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>45900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3566900</v>
+      </c>
+      <c r="E46" s="3">
         <v>6469200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4959600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5314900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6179300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5599200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5510700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6830500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6867000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7486100</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>116716900</v>
+      </c>
+      <c r="E47" s="3">
         <v>123654900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>121422100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>130118800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>119849100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>114757700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>110678000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>103437000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>101087600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>99642900</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>669600</v>
+      </c>
+      <c r="E48" s="3">
         <v>711200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1011100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1083500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1050600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1017700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1016400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>970900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>970500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>961300</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>516400</v>
+      </c>
+      <c r="E49" s="3">
         <v>528700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>517500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>554600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>509900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>494700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>507300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>422100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>423000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>395800</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1931,8 +2044,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1963,40 +2079,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27212200</v>
+      </c>
+      <c r="E52" s="3">
         <v>30456100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>25473700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27298200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24234900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23306300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22494000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21807600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21241200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21051100</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2027,40 +2149,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>149726000</v>
+      </c>
+      <c r="E54" s="3">
         <v>162895100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>153882500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>164904100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>152205200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>145522700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>140570900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>133776100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>130844200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>129789500</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2073,8 +2201,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2087,72 +2216,79 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>997100</v>
+      </c>
+      <c r="E57" s="3">
         <v>848200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>832900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>892600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>842600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>812200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>849300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>816900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>832000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>806700</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4719700</v>
+      </c>
+      <c r="E58" s="3">
         <v>6160200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8800</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>358600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2183,104 +2319,116 @@
       <c r="L59" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5786800</v>
+      </c>
+      <c r="E60" s="3">
         <v>7068300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>907400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>972400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>901800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>846700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1270900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>853300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>888500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>841200</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2173500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3755300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2831100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3033800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2858800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2843400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2074600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2060500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2072000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2078400</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>137575100</v>
+      </c>
+      <c r="E62" s="3">
         <v>147434400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>143570500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>153853400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>141489700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>135184700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>130474400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>124298900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>121256900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>120471800</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2311,8 +2459,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2343,8 +2494,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2375,40 +2529,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>145768400</v>
+      </c>
+      <c r="E66" s="3">
         <v>158515600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>147628400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>158202000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>145581700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>139197600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>134140000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>127534200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>124538400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>123710600</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2421,8 +2581,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2453,8 +2614,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2485,8 +2649,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2517,8 +2684,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2549,40 +2719,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3693200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3475000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3459000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3706800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3445400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3233200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3411900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3198300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3082000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2938400</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2613,8 +2789,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2645,8 +2824,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2677,40 +2859,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3957500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4379500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6227200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6673300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6599800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6303500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6410000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6222000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6286700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6060600</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2741,45 +2929,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44286</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44012</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43830</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43738</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2810,8 +3004,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2824,8 +3021,9 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -2856,8 +3054,11 @@
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2888,8 +3089,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2920,8 +3124,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2952,8 +3159,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2984,8 +3194,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3016,23 +3229,26 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E89" s="3">
+      <c r="E89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3">
         <v>1049800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1125000</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>4</v>
       </c>
@@ -3048,8 +3264,11 @@
       <c r="L89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3062,23 +3281,24 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="3">
+      <c r="E91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3700</v>
       </c>
-      <c r="G91" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H91" s="3" t="s">
         <v>4</v>
       </c>
@@ -3094,8 +3314,11 @@
       <c r="L91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3126,8 +3349,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3158,23 +3384,26 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E94" s="3">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1558400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1670100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H94" s="3" t="s">
         <v>4</v>
       </c>
@@ -3190,8 +3419,11 @@
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3204,22 +3436,23 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="E96" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
+      <c r="G96" s="3">
+        <v>0</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>4</v>
@@ -3236,8 +3469,11 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3268,8 +3504,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3300,8 +3539,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3332,23 +3574,26 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E100" s="3">
+      <c r="E100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1900</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>4</v>
       </c>
@@ -3364,8 +3609,11 @@
       <c r="L100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3396,8 +3644,11 @@
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -3405,14 +3656,14 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-502900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-539000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
         <v>0</v>
       </c>
@@ -3426,6 +3677,9 @@
         <v>0</v>
       </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>0</v>
       </c>
     </row>
